--- a/Test Cases- Contact list.xlsx
+++ b/Test Cases- Contact list.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68C49509-33DB-4418-BDC9-1990F2174B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC9FEE03-28D7-41D9-B671-30813C13A633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts-first half" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="296">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -165,6 +165,18 @@
     <t>the API recieved the request but did not accept it and gave status as expected</t>
   </si>
   <si>
+    <t>TC-CON-POST-005</t>
+  </si>
+  <si>
+    <t>send a POST request with an empty body to verify the validation of the server-side</t>
+  </si>
+  <si>
+    <t>No request body</t>
+  </si>
+  <si>
+    <t>the request sent, and the body returned a error in the fields, missing variables, validation Error messages, and the status 400 Bad request as expected</t>
+  </si>
+  <si>
     <t>TC-CON-GET-001</t>
   </si>
   <si>
@@ -175,9 +187,6 @@
   </si>
   <si>
     <t>GET</t>
-  </si>
-  <si>
-    <t>No request body</t>
   </si>
   <si>
     <t>Status 200 OK. Response body is an array containing at least one contact object with _id, firstName, and lastName</t>
@@ -367,6 +376,26 @@
 Response body: Error message indicating missing required fields (firstName, lastName).</t>
   </si>
   <si>
+    <t xml:space="preserve">TC-CON-PUT-007 </t>
+  </si>
+  <si>
+    <t>Attempts to update a deleted contact with valid, newly generated data for all fields.</t>
+  </si>
+  <si>
+    <t>Send POST /contacts to create a dummy contact. Set {{contactId}} to the response _id.
+Delete contactid</t>
+  </si>
+  <si>
+    <t>TC-CON-PUT-008</t>
+  </si>
+  <si>
+    <t>Attempts to modifiy a user conatct with valid data while they was log out</t>
+  </si>
+  <si>
+    <t>Send POST /contacts to create a dummy contact. Set {{contactId}} to the response _id.
+Log out contactid</t>
+  </si>
+  <si>
     <t>TC-CON-PATCH-001</t>
   </si>
   <si>
@@ -402,7 +431,7 @@
     <t>TC-CON-PATCH-003</t>
   </si>
   <si>
-    <t>Send POST /contacts to create a dummy contact. 
+    <t>Send POST /contacts to create a dummy contact.
 Set {{contactId}}.
 Set {invaild_token}.</t>
   </si>
@@ -424,6 +453,15 @@
     <t>Fail</t>
   </si>
   <si>
+    <t>TC-CON-PATCH-005</t>
+  </si>
+  <si>
+    <t>Attempts to patch a deleted contact with valid, newly generated data for all fields.</t>
+  </si>
+  <si>
+    <t>TC-CON-PATCH-006</t>
+  </si>
+  <si>
     <t>TC-CON-DEL-001</t>
   </si>
   <si>
@@ -441,6 +479,9 @@
   </si>
   <si>
     <t>TC-CON-DEL-002</t>
+  </si>
+  <si>
+    <t>Attempt to delete a contact ID that does not exist.</t>
   </si>
   <si>
     <t>Status Code: 404 Not Found
@@ -496,6 +537,9 @@
     <t>Bearer {token}}</t>
   </si>
   <si>
+    <t> </t>
+  </si>
+  <si>
     <t>TC-UR-POST-001</t>
   </si>
   <si>
@@ -1541,6 +1585,98 @@
   </si>
   <si>
     <t>{"lastName": 2.9}</t>
+  </si>
+  <si>
+    <t>TC-UR-PATCH-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update a user that don't exsit </t>
+  </si>
+  <si>
+    <t>User never existed</t>
+  </si>
+  <si>
+    <t>InValid Bearer Token</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Status Code: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">401 Unauthorized , </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Response body:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> error message</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Status Code:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 401 Unauthorized , </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Response body:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> error message</t>
+    </r>
   </si>
   <si>
     <t>Authorization</t>
@@ -1757,7 +1893,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1786,12 +1922,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -1839,12 +1969,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
@@ -1865,6 +1989,52 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF375623"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1874,7 +2044,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1962,11 +2132,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1982,9 +2200,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2017,44 +2232,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2064,14 +2273,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2079,14 +2282,122 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2402,7 +2713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.140625" bestFit="1" customWidth="1"/>
@@ -2449,296 +2760,324 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="317.25" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="25" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="106.5">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="J3" s="26" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="121.5">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="26" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="121.5">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="121.5">
-      <c r="A6" s="9" t="s">
+      <c r="J5" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="152.25">
+      <c r="A6" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="H6" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="121.5">
+      <c r="A7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="E7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="106.5">
-      <c r="A7" s="9" t="s">
+      <c r="G7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="106.5">
+      <c r="A8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="F8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="106.5">
+      <c r="A9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="121.5">
+      <c r="A10" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="106.5">
-      <c r="A8" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="121.5">
-      <c r="A9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="121.5">
+      <c r="A11" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="121.5">
-      <c r="A10" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="30" t="s">
+      <c r="E11" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="4"/>
-      <c r="B11" s="3"/>
+      <c r="G11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4"/>
@@ -2759,6 +3098,10 @@
     <row r="16" spans="1:10">
       <c r="A16" s="4"/>
       <c r="B16" s="3"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="4"/>
+      <c r="B17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2767,562 +3110,695 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC0CDAC-F217-4C19-AFB9-BFC9359E2CD1}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="46.7109375" style="16" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" style="16" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="15" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="33.140625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="28" style="12" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="15" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="46.7109375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" style="15" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="14" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="33.140625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="28" style="54" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="139.5" customHeight="1">
-      <c r="A2" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="17" t="s">
+      <c r="A2" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" s="17" t="s">
+      <c r="E2" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="F2" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="J2" s="55" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="81.75" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="45.75">
+      <c r="A4" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="60.75">
+      <c r="A5" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="45.75">
+      <c r="A6" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60.75">
+      <c r="A7" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="137.25">
+      <c r="A8" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="H8" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="J8" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="137.25">
+      <c r="A9" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="H3" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="I3" s="17" t="s">
+      <c r="E9" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="J3" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="45.75">
-      <c r="A4" s="17" t="s">
+      <c r="F9" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60.75">
+      <c r="A10" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="40" t="s">
+      <c r="D10" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="I10" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60.75">
+      <c r="A11" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="I11" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="60.75">
+      <c r="A12" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="H4" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="60.75">
-      <c r="A5" s="17" t="s">
+      <c r="C12" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="E12" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="I12" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="45.75">
+      <c r="A13" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="H5" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J5" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="45.75">
-      <c r="A6" s="17" t="s">
+      <c r="E13" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="I13" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="J13" s="57" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="60.75">
+      <c r="A14" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J14" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="60.75">
+      <c r="A15" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="60.75">
+      <c r="A16" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J16" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="60.75">
+      <c r="A17" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="D17" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" s="17" t="s">
+      <c r="G17" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="I17" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="J17" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="91.5">
+      <c r="A18" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="H6" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="60.75">
-      <c r="A7" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="E18" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="J18" s="58" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="76.5">
+      <c r="A19" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="I19" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="60.75">
-      <c r="A8" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="J19" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="60.75">
+      <c r="A20" s="60" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="I20" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="H8" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="60.75">
-      <c r="A9" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="60.75">
-      <c r="A10" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="H10" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="45.75">
-      <c r="A11" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="H11" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="J11" s="41" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="60.75">
-      <c r="A12" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H12" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="60.75">
-      <c r="A13" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H13" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J13" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="91.5">
-      <c r="A14" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H14" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="J14" s="42" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="76.5">
-      <c r="A15" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H15" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="60.75">
-      <c r="A16" s="17" t="s">
+      <c r="J20" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="121.5">
+      <c r="A21" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="B21" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21" s="52" t="s">
         <v>127</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="F21" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H16" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J16" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="121.5">
-      <c r="A17" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H17" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="I17" s="17"/>
-      <c r="J17" s="31" t="s">
-        <v>19</v>
-      </c>
+      <c r="H21" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="J21" s="56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3334,636 +3810,666 @@
   <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" customWidth="1"/>
-    <col min="3" max="4" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" style="40" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="15" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="40.140625" customWidth="1"/>
+    <col min="7" max="7" width="40.140625" style="14" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.5">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="34" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="60.75">
-      <c r="A2" s="17" t="s">
-        <v>134</v>
+      <c r="A2" s="16" t="s">
+        <v>148</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>138</v>
+      <c r="F2" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="J2" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="J2" s="24" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="91.5">
-      <c r="A3" s="17" t="s">
-        <v>142</v>
+      <c r="A3" s="16" t="s">
+        <v>156</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>138</v>
+      <c r="F3" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="I3" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="J3" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="J3" s="24" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="60.75">
-      <c r="A4" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="A4" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>138</v>
+      <c r="F4" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="G4" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="60.75">
+      <c r="A5" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="E5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="60.75">
-      <c r="A5" s="17" t="s">
+      <c r="G5" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60.75">
+      <c r="A6" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60.75">
+      <c r="A7" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="I5" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="60.75">
-      <c r="A6" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="60.75">
-      <c r="A7" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="J7" s="19" t="s">
+      <c r="I7" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="J7" s="17" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="76.5">
-      <c r="A8" s="17" t="s">
-        <v>163</v>
+      <c r="A8" s="16" t="s">
+        <v>177</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="76.5">
+      <c r="A9" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="76.5">
+      <c r="A10" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="91.5">
+      <c r="A11" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="91.5">
+      <c r="A12" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="106.5">
+      <c r="A13" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="H13" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H8" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="76.5">
-      <c r="A9" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="76.5">
-      <c r="A10" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="91.5">
-      <c r="A11" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="I13" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="106.5">
+      <c r="A14" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="H14" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="91.5">
-      <c r="A12" s="17" t="s">
+      <c r="I14" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="121.5">
+      <c r="A15" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="E15" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="G15" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="117" customHeight="1">
+      <c r="A16" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="J16" s="24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="76.5">
+      <c r="A17" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="76.5">
+      <c r="A18" s="61" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>218</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="E18" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" s="62" t="s">
+        <v>181</v>
+      </c>
+      <c r="G18" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="H18" s="64" t="s">
+        <v>220</v>
+      </c>
+      <c r="I18" s="65" t="s">
         <v>182</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="106.5">
-      <c r="A13" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="J18" s="66" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="93.75" customHeight="1">
+      <c r="A19" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I19" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="J13" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="106.5">
-      <c r="A14" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="121.5">
-      <c r="A15" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H15" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="J15" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="117" customHeight="1">
-      <c r="A16" s="17" t="s">
+      <c r="J19" s="66" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="60.75">
+      <c r="A20" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C20" s="70" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G20" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="H16" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="J16" s="26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="76.5">
-      <c r="A17" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="J17" s="26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="76.5">
-      <c r="A18" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="J18" s="27" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="93.75" customHeight="1">
-      <c r="A19" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="I19" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="J19" s="27" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="5"/>
+      <c r="H20" s="68" t="s">
+        <v>228</v>
+      </c>
+      <c r="I20" s="73" t="s">
+        <v>229</v>
+      </c>
+      <c r="J20" s="72" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="5"/>
+      <c r="A21" s="14"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="5"/>
+      <c r="A22" s="14"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="5"/>
+      <c r="A23" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3975,9 +4481,9 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
-    <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" style="42" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" customWidth="1"/>
     <col min="5" max="6" width="14.42578125" customWidth="1"/>
     <col min="7" max="7" width="33.28515625" customWidth="1"/>
@@ -3986,17 +4492,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -4013,647 +4519,647 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="32" t="s">
+      <c r="J1" s="29" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="49.5" customHeight="1">
-      <c r="A2" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="E2" s="20" t="s">
+      <c r="A2" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J2" s="31" t="s">
+      <c r="F2" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J2" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75">
-      <c r="A3" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="A3" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="I3" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J3" s="31" t="s">
+      <c r="F3" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J3" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75">
-      <c r="A4" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="E4" s="20" t="s">
+      <c r="A4" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J4" s="31" t="s">
+      <c r="F4" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J4" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75">
-      <c r="A5" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="E5" s="20" t="s">
+      <c r="A5" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>245</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="I5" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J5" s="31" t="s">
+      <c r="F5" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J5" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30.75">
-      <c r="A6" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="E6" s="20" t="s">
+      <c r="A6" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="I6" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J6" s="31" t="s">
+      <c r="F6" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J6" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30.75">
-      <c r="A7" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="30.75">
+      <c r="A8" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="76.5">
+      <c r="A9" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="76.5">
+      <c r="A10" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="76.5">
+      <c r="A11" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="I11" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="60.75">
+      <c r="A12" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="I12" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="76.5">
+      <c r="A13" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="I13" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75">
+      <c r="A14" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="I14" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="45.75">
+      <c r="A15" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="C7" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="I7" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="30.75">
-      <c r="A8" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="E15" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="I15" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="I8" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="76.5">
-      <c r="A9" s="20" t="s">
+      <c r="J15" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75">
+      <c r="A16" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="E16" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="C9" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="I16" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75">
+      <c r="A17" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="I9" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="76.5">
-      <c r="A10" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="B10" s="21" t="s">
+      <c r="E17" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="I17" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.75">
+      <c r="A18" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="C18" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="I10" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="91.5">
-      <c r="A11" s="20" t="s">
+      <c r="D18" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="E18" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="C11" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="I11" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J11" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="60.75">
-      <c r="A12" s="20" t="s">
+      <c r="I18" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="30.75">
+      <c r="A19" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="I12" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="76.5">
-      <c r="A13" s="20" t="s">
+      <c r="E19" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I19" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="30.75">
+      <c r="A20" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="B13" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="I13" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J13" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15.75">
-      <c r="A14" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="B14" s="21" t="s">
+      <c r="E20" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="I20" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J20" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30.75">
+      <c r="A21" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="D21" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="C14" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="I14" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="45.75">
-      <c r="A15" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="I15" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J15" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15.75">
-      <c r="A16" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H16" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="I16" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J16" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15.75">
-      <c r="A17" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="I17" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J17" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15.75">
-      <c r="A18" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="I18" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J18" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="30.75">
-      <c r="A19" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="I19" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J19" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="30.75">
-      <c r="A20" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="I20" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J20" s="31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="30.75">
-      <c r="A21" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="I21" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J21" s="31" t="s">
+      <c r="E21" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I21" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="J21" s="28" t="s">
         <v>19</v>
       </c>
     </row>
